--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="263">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -763,6 +763,9 @@
     <t xml:space="preserve">WYCLIFFE WAFULA</t>
   </si>
   <si>
+    <t xml:space="preserve">TH47UI0TXH </t>
+  </si>
+  <si>
     <t xml:space="preserve">25/07/2025</t>
   </si>
   <si>
@@ -803,6 +806,9 @@
   </si>
   <si>
     <t xml:space="preserve">TIMOTHY MUCHERU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH26J2JUU6 </t>
   </si>
   <si>
     <t xml:space="preserve">31/7/2025</t>
@@ -849,7 +855,7 @@
     <numFmt numFmtId="167" formatCode="0;[RED]0"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,6 +957,14 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <color rgb="FFFFA500"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
       <color rgb="FF008000"/>
       <name val="Georgia"/>
       <family val="1"/>
@@ -977,9 +991,24 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FFFFA500"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FFFFA500"/>
       <name val="Georgia"/>
       <family val="1"/>
       <charset val="1"/>
@@ -1041,7 +1070,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1126,6 +1155,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1134,19 +1167,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1154,11 +1179,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1166,11 +1211,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1229,7 +1274,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFFA500"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
@@ -4586,7 +4631,7 @@
       <c r="F3" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G3" s="19" t="n">
+      <c r="G3" s="20" t="n">
         <v>32000</v>
       </c>
       <c r="H3" s="16" t="s">
@@ -4600,26 +4645,26 @@
       <c r="A4" s="18" t="n">
         <v>102</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="21" t="n">
         <v>37907779</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="21" t="n">
         <v>795778727</v>
       </c>
-      <c r="E4" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22" t="n">
+      <c r="E4" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24" t="n">
         <v>32300</v>
       </c>
-      <c r="H4" s="23" t="n">
+      <c r="H4" s="25" t="n">
         <v>45665</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="21" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4627,28 +4672,28 @@
       <c r="A5" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="21" t="n">
         <v>22203283</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>734601433</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -4657,30 +4702,30 @@
       <c r="F6" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
         <v>105</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="18" t="n">
         <v>32000</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G7" s="19" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H7" s="25" t="n">
+      <c r="G7" s="20" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H7" s="27" t="n">
         <v>45665</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="21" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4688,47 +4733,47 @@
       <c r="A8" s="18" t="n">
         <v>106</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>26007698</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>712618128</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
+      <c r="E8" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G8" s="24"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="n">
         <v>201</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="21" t="n">
         <v>28689105</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>726391968</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -4737,21 +4782,21 @@
       <c r="F10" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="n">
         <v>202</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="21" t="n">
         <v>34497236</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>7997082120</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -4760,21 +4805,21 @@
       <c r="F11" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="20"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
         <v>203</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="29" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="21" t="n">
         <v>26743529</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>740351187</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -4783,21 +4828,21 @@
       <c r="F12" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
         <v>204</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="21" t="n">
         <v>37925531</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>757891600</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -4806,78 +4851,78 @@
       <c r="F13" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G13" s="22"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
         <v>205</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>7417077875</v>
       </c>
-      <c r="E14" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G14" s="22"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
+      <c r="E14" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G14" s="24"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
         <v>206</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>23406138</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>757560344</v>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="22" t="n">
         <v>32000</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G15" s="22"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
         <v>301</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <v>32437159</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="21" t="n">
         <v>724856002</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -4886,217 +4931,223 @@
       <c r="F17" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="n">
         <v>302</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="21" t="n">
         <v>25074051</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="21" t="n">
         <v>724779438</v>
       </c>
-      <c r="E18" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="20"/>
+      <c r="E18" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="n">
         <v>303</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="21" t="n">
         <v>28508205</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="21" t="n">
         <v>724782185</v>
       </c>
-      <c r="E19" s="21" t="n">
+      <c r="E19" s="22" t="n">
         <v>32000</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="20"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
         <v>304</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="21" t="n">
         <v>672131885</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="21" t="n">
         <v>795141552</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>32000</v>
       </c>
       <c r="F20" s="19"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="20"/>
+      <c r="G20" s="24" t="n">
+        <v>34270</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="n">
         <v>305</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20" t="n">
+      <c r="C21" s="21"/>
+      <c r="D21" s="21" t="n">
         <v>723701190</v>
       </c>
-      <c r="E21" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="E21" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G21" s="24"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="n">
         <v>306</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="21" t="n">
         <v>39846944</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="21" t="n">
         <v>795224557</v>
       </c>
-      <c r="E22" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F22" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="20"/>
+      <c r="E22" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G22" s="24"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="n">
         <v>401</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="21" t="n">
         <v>29807634</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="21" t="n">
         <v>703138775</v>
       </c>
-      <c r="E24" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F24" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
+      <c r="E24" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G24" s="24"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="n">
         <v>402</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="21" t="n">
         <v>34785180</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="21" t="n">
         <v>728325855</v>
       </c>
-      <c r="E25" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="E25" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
         <v>403</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="21" t="n">
         <v>22248984</v>
       </c>
-      <c r="D26" s="20" t="n">
+      <c r="D26" s="21" t="n">
         <v>718933881</v>
       </c>
-      <c r="E26" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="E26" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G26" s="24"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="n">
         <v>404</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="21" t="n">
         <v>34409807</v>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="21" t="n">
         <v>712665837</v>
       </c>
-      <c r="E27" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="20"/>
+      <c r="E27" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="21"/>
       <c r="J27" s="16" t="n">
         <v>450</v>
       </c>
@@ -5105,99 +5156,99 @@
       <c r="A28" s="18" t="n">
         <v>405</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="21" t="n">
         <v>26353461</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="21" t="n">
         <v>701116277</v>
       </c>
-      <c r="E28" s="21" t="n">
+      <c r="E28" s="22" t="n">
         <v>32000</v>
       </c>
       <c r="F28" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="n">
         <v>406</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="21" t="n">
         <v>32179785</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="21" t="n">
         <v>720334200</v>
       </c>
-      <c r="E29" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
+      <c r="E29" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F29" s="23"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="18"/>
       <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="n">
         <v>501</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="21" t="n">
         <v>797982879</v>
       </c>
-      <c r="E31" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="20"/>
+      <c r="E31" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F31" s="23"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
         <v>502</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="B32" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="21" t="n">
         <v>328595524</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="21" t="n">
         <v>798082750</v>
       </c>
-      <c r="E32" s="21" t="n">
+      <c r="E32" s="22" t="n">
         <v>30500</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28" t="n">
+      <c r="F32" s="23"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5205,49 +5256,49 @@
       <c r="A33" s="18" t="n">
         <v>503</v>
       </c>
-      <c r="B33" s="20" t="s">
+      <c r="B33" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="21" t="n">
         <v>36909475</v>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="21" t="n">
         <v>708822190</v>
       </c>
-      <c r="E33" s="21" t="n">
+      <c r="E33" s="22" t="n">
         <v>32000</v>
       </c>
       <c r="F33" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G33" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="I33" s="20" t="s">
+      <c r="G33" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H33" s="21" t="s">
         <v>237</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="n">
         <v>504</v>
       </c>
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20" t="s">
+      <c r="C34" s="21"/>
+      <c r="D34" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="E34" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="20"/>
+      <c r="E34" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F34" s="31"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="21"/>
       <c r="J34" s="16" t="n">
         <v>450</v>
       </c>
@@ -5256,295 +5307,295 @@
       <c r="A35" s="18" t="n">
         <v>505</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="21" t="n">
         <v>32942992</v>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="21" t="n">
         <v>711236179</v>
       </c>
-      <c r="E35" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="22" t="n">
+      <c r="E35" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F35" s="31"/>
+      <c r="G35" s="24" t="n">
         <v>32300</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="I35" s="20" t="s">
+      <c r="H35" s="25" t="s">
         <v>239</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="n">
         <v>506</v>
       </c>
-      <c r="B36" s="20" t="s">
+      <c r="B36" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="21" t="n">
         <v>30208195</v>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="21" t="n">
         <v>708860250</v>
       </c>
-      <c r="E36" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="20"/>
+      <c r="E36" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F36" s="31"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="n">
         <v>601</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="21" t="n">
         <v>31017350</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="21" t="n">
         <v>722138646</v>
       </c>
-      <c r="E38" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F38" s="28"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="20"/>
+      <c r="E38" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F38" s="31"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="n">
         <v>602</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="C39" s="20" t="n">
+      <c r="B39" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="21" t="n">
         <v>385353317</v>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="21" t="n">
         <v>110147006</v>
       </c>
-      <c r="E39" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="20"/>
+      <c r="E39" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F39" s="31"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="n">
         <v>603</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="21" t="n">
         <v>29596759</v>
       </c>
-      <c r="D40" s="20" t="n">
+      <c r="D40" s="21" t="n">
         <v>721967235</v>
       </c>
-      <c r="E40" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F40" s="28"/>
-      <c r="G40" s="22" t="n">
+      <c r="E40" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F40" s="31"/>
+      <c r="G40" s="24" t="n">
         <v>32300</v>
       </c>
-      <c r="H40" s="25" t="n">
+      <c r="H40" s="27" t="n">
         <v>45665</v>
       </c>
-      <c r="I40" s="20" t="s">
-        <v>241</v>
+      <c r="I40" s="21" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="n">
         <v>604</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20" t="n">
+      <c r="C41" s="21"/>
+      <c r="D41" s="21" t="n">
         <v>723482227</v>
       </c>
-      <c r="E41" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F41" s="28"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="20"/>
+      <c r="E41" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F41" s="31"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="n">
         <v>605</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="21" t="n">
         <v>28497464</v>
       </c>
-      <c r="D42" s="20" t="n">
+      <c r="D42" s="21" t="n">
         <v>729584979</v>
       </c>
-      <c r="E42" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
+      <c r="E42" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F42" s="31"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="n">
         <v>606</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="21" t="n">
         <v>36635011</v>
       </c>
-      <c r="D43" s="20" t="n">
+      <c r="D43" s="21" t="n">
         <v>700208592</v>
       </c>
-      <c r="E43" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F43" s="28"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="20"/>
+      <c r="E43" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F43" s="31"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="18"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="n">
         <v>701</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="21" t="n">
         <v>36723204</v>
       </c>
-      <c r="D45" s="20" t="n">
+      <c r="D45" s="21" t="n">
         <v>743552330</v>
       </c>
-      <c r="E45" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F45" s="28"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="20"/>
+      <c r="E45" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F45" s="31"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="n">
         <v>702</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="21" t="n">
         <v>32736219</v>
       </c>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="21" t="n">
         <v>705021087</v>
       </c>
-      <c r="E46" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F46" s="28"/>
-      <c r="G46" s="29" t="n">
+      <c r="E46" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F46" s="31"/>
+      <c r="G46" s="33" t="n">
         <v>32400</v>
       </c>
-      <c r="H46" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="I46" s="30" t="s">
+      <c r="H46" s="34" t="s">
         <v>243</v>
+      </c>
+      <c r="I46" s="34" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="n">
         <v>703</v>
       </c>
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20" t="n">
+      <c r="C47" s="21"/>
+      <c r="D47" s="21" t="n">
         <v>717982212</v>
       </c>
-      <c r="E47" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F47" s="28"/>
-      <c r="G47" s="22" t="n">
+      <c r="E47" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F47" s="31"/>
+      <c r="G47" s="24" t="n">
         <v>35300</v>
       </c>
-      <c r="H47" s="23" t="n">
+      <c r="H47" s="25" t="n">
         <v>45665</v>
       </c>
-      <c r="I47" s="20" t="s">
-        <v>244</v>
+      <c r="I47" s="21" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="n">
         <v>704</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="21" t="n">
         <v>27424733</v>
       </c>
-      <c r="D48" s="20" t="n">
+      <c r="D48" s="21" t="n">
         <v>741497042</v>
       </c>
-      <c r="E48" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F48" s="28"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
+      <c r="E48" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F48" s="31"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
       <c r="J48" s="16" t="n">
         <v>600</v>
       </c>
@@ -5553,477 +5604,483 @@
       <c r="A49" s="18" t="n">
         <v>705</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="C49" s="20" t="n">
+      <c r="B49" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C49" s="21" t="n">
         <v>27541354</v>
       </c>
-      <c r="D49" s="20" t="n">
+      <c r="D49" s="21" t="n">
         <v>725535858</v>
       </c>
-      <c r="E49" s="21" t="n">
+      <c r="E49" s="22" t="n">
         <v>30500</v>
       </c>
-      <c r="F49" s="28"/>
-      <c r="G49" s="22" t="n">
+      <c r="F49" s="31"/>
+      <c r="G49" s="24" t="n">
         <v>31200</v>
       </c>
-      <c r="H49" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="I49" s="20" t="s">
+      <c r="H49" s="25" t="s">
         <v>247</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="n">
         <v>706</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="21" t="n">
         <v>26286733</v>
       </c>
-      <c r="D50" s="20" t="n">
+      <c r="D50" s="21" t="n">
         <v>707947316</v>
       </c>
-      <c r="E50" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28" t="n">
+      <c r="E50" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F50" s="31"/>
+      <c r="G50" s="24" t="n">
         <v>32400</v>
       </c>
-      <c r="H50" s="25" t="n">
+      <c r="H50" s="27" t="n">
         <v>45665</v>
       </c>
-      <c r="I50" s="20" t="s">
-        <v>248</v>
+      <c r="I50" s="21" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
       <c r="E51" s="18"/>
-      <c r="F51" s="20"/>
+      <c r="F51" s="32"/>
       <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="18" t="n">
         <v>801</v>
       </c>
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="21" t="n">
         <v>29439632</v>
       </c>
-      <c r="D52" s="20" t="n">
+      <c r="D52" s="21" t="n">
         <v>724838245</v>
       </c>
-      <c r="E52" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F52" s="28"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="20"/>
+      <c r="E52" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F52" s="31"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="n">
         <v>802</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C53" s="20" t="n">
+      <c r="C53" s="21" t="n">
         <v>32411862</v>
       </c>
-      <c r="D53" s="20" t="n">
+      <c r="D53" s="21" t="n">
         <v>720229325</v>
       </c>
-      <c r="E53" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="20"/>
+      <c r="E53" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F53" s="31"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="25"/>
+      <c r="I53" s="21"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="n">
         <v>803</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C54" s="21" t="n">
         <v>41559757</v>
       </c>
-      <c r="D54" s="20" t="n">
+      <c r="D54" s="21" t="n">
         <v>704498777</v>
       </c>
-      <c r="E54" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="20"/>
+      <c r="E54" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F54" s="31"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="25"/>
+      <c r="I54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="n">
         <v>804</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="20" t="n">
+      <c r="C55" s="21" t="n">
         <v>36813656</v>
       </c>
-      <c r="D55" s="20" t="n">
+      <c r="D55" s="21" t="n">
         <v>796828986</v>
       </c>
-      <c r="E55" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
+      <c r="E55" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F55" s="31"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="n">
         <v>805</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="C56" s="20" t="n">
+      <c r="B56" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C56" s="21" t="n">
         <v>25144649</v>
       </c>
-      <c r="D56" s="20" t="n">
+      <c r="D56" s="21" t="n">
         <v>726319801</v>
       </c>
-      <c r="E56" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
+      <c r="E56" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F56" s="31"/>
+      <c r="G56" s="24" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H56" s="27" t="n">
+        <v>45696</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="n">
         <v>806</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="20" t="n">
+      <c r="C57" s="21" t="n">
         <v>40361306</v>
       </c>
-      <c r="D57" s="20" t="n">
+      <c r="D57" s="21" t="n">
         <v>791229029</v>
       </c>
-      <c r="E57" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="20"/>
+      <c r="E57" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F57" s="31"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="21"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
       <c r="E58" s="18"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="18" t="n">
         <v>901</v>
       </c>
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="20" t="n">
+      <c r="C59" s="21" t="n">
         <v>35580923</v>
       </c>
-      <c r="D59" s="20" t="n">
+      <c r="D59" s="21" t="n">
         <v>702602056</v>
       </c>
-      <c r="E59" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="23"/>
-      <c r="I59" s="20"/>
+      <c r="E59" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F59" s="31"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="18" t="n">
         <v>902</v>
       </c>
-      <c r="B60" s="20" t="s">
+      <c r="B60" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="20" t="n">
+      <c r="C60" s="21" t="n">
         <v>28068761</v>
       </c>
-      <c r="D60" s="20" t="n">
+      <c r="D60" s="21" t="n">
         <v>721178178</v>
       </c>
-      <c r="E60" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="23"/>
-      <c r="I60" s="20"/>
+      <c r="E60" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F60" s="31"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="n">
         <v>903</v>
       </c>
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="20" t="n">
+      <c r="C61" s="21" t="n">
         <v>30446277</v>
       </c>
-      <c r="D61" s="20" t="s">
+      <c r="D61" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="E61" s="21" t="n">
+      <c r="E61" s="22" t="n">
         <v>30500</v>
       </c>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="23"/>
-      <c r="I61" s="20"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="21"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="18" t="n">
         <v>904</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C62" s="21" t="n">
         <v>29490404</v>
       </c>
-      <c r="D62" s="20" t="n">
+      <c r="D62" s="21" t="n">
         <v>727692378</v>
       </c>
-      <c r="E62" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
+      <c r="E62" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F62" s="31"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
         <v>905</v>
       </c>
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20" t="n">
+      <c r="C63" s="21"/>
+      <c r="D63" s="21" t="n">
         <v>727826667</v>
       </c>
-      <c r="E63" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="20"/>
+      <c r="E63" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F63" s="31"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="21"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="n">
         <v>906</v>
       </c>
-      <c r="B64" s="20" t="s">
+      <c r="B64" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C64" s="20" t="n">
+      <c r="C64" s="21" t="n">
         <v>36519977</v>
       </c>
-      <c r="D64" s="20" t="n">
+      <c r="D64" s="21" t="n">
         <v>748908722</v>
       </c>
-      <c r="E64" s="21" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F64" s="28"/>
-      <c r="G64" s="22"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="20"/>
+      <c r="E64" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F64" s="31"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="21"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="18"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="28"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="20" t="s">
+      <c r="B66" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="D66" s="20" t="n">
+      <c r="D66" s="21" t="n">
         <v>743853830</v>
       </c>
-      <c r="E66" s="21" t="n">
+      <c r="E66" s="22" t="n">
         <v>26000</v>
       </c>
-      <c r="F66" s="28"/>
-      <c r="G66" s="22" t="n">
+      <c r="F66" s="31"/>
+      <c r="G66" s="24" t="n">
         <v>29450</v>
       </c>
-      <c r="H66" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="I66" s="20" t="s">
-        <v>251</v>
+      <c r="H66" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="I66" s="21" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="18"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
       <c r="E67" s="18" t="n">
         <f aca="false">SUM(E3:E66)</f>
         <v>1685500</v>
       </c>
-      <c r="F67" s="32" t="n">
+      <c r="F67" s="35" t="n">
         <f aca="false">SUM(F3:F66)</f>
         <v>576000</v>
       </c>
-      <c r="G67" s="32" t="n">
+      <c r="G67" s="36" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>353650</v>
-      </c>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
+        <v>423220</v>
+      </c>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
       <c r="J67" s="16" t="n">
         <f aca="false">SUM(J3:J66)</f>
         <v>1950</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
+      <c r="A68" s="21"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
+      <c r="A69" s="21"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
+      <c r="A70" s="21"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="20"/>
-      <c r="B71" s="20" t="s">
+      <c r="A71" s="21"/>
+      <c r="B71" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="20" t="n">
+      <c r="C71" s="21" t="n">
         <v>544000</v>
       </c>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20" t="s">
+      <c r="A72" s="21"/>
+      <c r="B72" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="20" t="n">
+      <c r="C72" s="21" t="n">
         <v>1642300</v>
       </c>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20"/>
-      <c r="B73" s="20"/>
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
       <c r="C73" s="18" t="n">
         <f aca="false">SUM(C71:C72)</f>
         <v>2186300</v>
       </c>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
+      <c r="A74" s="21"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6083,7 +6140,7 @@
         <v>795778727</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6233,7 +6290,7 @@
         <v>728325855</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6257,7 +6314,7 @@
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>701116277</v>
@@ -6301,7 +6358,7 @@
         <v>503</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>708822190</v>
@@ -6351,7 +6408,7 @@
         <v>722138646</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6387,7 +6444,7 @@
         <v>723482227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6500,7 +6557,7 @@
         <v>720229325</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6530,7 +6587,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>726319801</v>
@@ -6613,7 +6670,7 @@
         <v>748908722</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="269">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -760,18 +760,33 @@
     <t xml:space="preserve">TGI0HP2QKU</t>
   </si>
   <si>
+    <t xml:space="preserve">TH48XE8MQ0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH25LAM5R5 </t>
+  </si>
+  <si>
     <t xml:space="preserve">WYCLIFFE WAFULA</t>
   </si>
   <si>
+    <t xml:space="preserve">TH45XGJDCH</t>
+  </si>
+  <si>
     <t xml:space="preserve">TH47UI0TXH </t>
   </si>
   <si>
+    <t xml:space="preserve">TH35R3PLBD </t>
+  </si>
+  <si>
     <t xml:space="preserve">25/07/2025</t>
   </si>
   <si>
     <t xml:space="preserve">TGP8IMG3WW </t>
   </si>
   <si>
+    <t xml:space="preserve">TH57XU1DIR </t>
+  </si>
+  <si>
     <t xml:space="preserve">30/07/2025</t>
   </si>
   <si>
@@ -809,6 +824,9 @@
   </si>
   <si>
     <t xml:space="preserve">TH26J2JUU6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH44V0HDVC </t>
   </si>
   <si>
     <t xml:space="preserve">31/7/2025</t>
@@ -855,7 +873,7 @@
     <numFmt numFmtId="167" formatCode="0;[RED]0"/>
     <numFmt numFmtId="168" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -971,6 +989,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Georgia"/>
@@ -1070,7 +1095,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1156,6 +1181,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1172,30 +1201,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1203,19 +1220,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4612,7 +4645,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="n">
         <v>101</v>
       </c>
@@ -4634,66 +4667,66 @@
       <c r="G3" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="21" t="s">
         <v>231</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="n">
         <v>102</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="22" t="n">
         <v>37907779</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="22" t="n">
         <v>795778727</v>
       </c>
-      <c r="E4" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24" t="n">
+      <c r="E4" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F4" s="24"/>
+      <c r="G4" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H4" s="25" t="n">
+      <c r="H4" s="26" t="n">
         <v>45665</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="22" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
       <c r="E5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="24"/>
       <c r="G5" s="20"/>
       <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
         <v>104</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="22" t="n">
         <v>22203283</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="22" t="n">
         <v>734601433</v>
       </c>
       <c r="E6" s="18" t="n">
@@ -4703,16 +4736,16 @@
         <v>32000</v>
       </c>
       <c r="G6" s="20"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="26"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
         <v>105</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
       <c r="E7" s="18" t="n">
         <v>32000</v>
       </c>
@@ -4722,58 +4755,64 @@
       <c r="G7" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="28" t="n">
         <v>45665</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="22" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="n">
         <v>106</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="22" t="n">
         <v>26007698</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <v>712618128</v>
       </c>
-      <c r="E8" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>32600</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
       <c r="G9" s="20"/>
       <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="n">
         <v>201</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C10" s="22" t="n">
         <v>28689105</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="22" t="n">
         <v>726391968</v>
       </c>
       <c r="E10" s="18" t="n">
@@ -4783,20 +4822,20 @@
         <v>32000</v>
       </c>
       <c r="G10" s="20"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="21"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="26"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="n">
         <v>202</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="22" t="n">
         <v>34497236</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>7997082120</v>
       </c>
       <c r="E11" s="18" t="n">
@@ -4805,21 +4844,27 @@
       <c r="F11" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G11" s="28"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="21"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G11" s="29" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>45696</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
         <v>203</v>
       </c>
-      <c r="B12" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="22" t="n">
         <v>26743529</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>740351187</v>
       </c>
       <c r="E12" s="18" t="n">
@@ -4830,19 +4875,19 @@
       </c>
       <c r="G12" s="20"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="n">
         <v>204</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="22" t="n">
         <v>37925531</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>757891600</v>
       </c>
       <c r="E13" s="18" t="n">
@@ -4851,78 +4896,78 @@
       <c r="F13" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G13" s="24"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="n">
         <v>205</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>7417077875</v>
       </c>
-      <c r="E14" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G14" s="24"/>
+      <c r="E14" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G14" s="25"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
         <v>206</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="22" t="n">
         <v>23406138</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="22" t="n">
         <v>757560344</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="23" t="n">
         <v>32000</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19"/>
       <c r="G16" s="20"/>
       <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="n">
         <v>301</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="22" t="n">
         <v>32437159</v>
       </c>
-      <c r="D17" s="21" t="n">
+      <c r="D17" s="22" t="n">
         <v>724856002</v>
       </c>
       <c r="E17" s="18" t="n">
@@ -4931,1156 +4976,1180 @@
       <c r="F17" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G17" s="24"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G17" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="n">
         <v>302</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="22" t="n">
         <v>25074051</v>
       </c>
-      <c r="D18" s="21" t="n">
+      <c r="D18" s="22" t="n">
         <v>724779438</v>
       </c>
-      <c r="E18" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="21"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F18" s="24"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="22"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="n">
         <v>303</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="22" t="n">
         <v>28508205</v>
       </c>
-      <c r="D19" s="21" t="n">
+      <c r="D19" s="22" t="n">
         <v>724782185</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="23" t="n">
         <v>32000</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G19" s="24"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="21"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G19" s="25"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
         <v>304</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="22" t="n">
         <v>672131885</v>
       </c>
-      <c r="D20" s="21" t="n">
+      <c r="D20" s="22" t="n">
         <v>795141552</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>32000</v>
       </c>
       <c r="F20" s="19"/>
-      <c r="G20" s="24" t="n">
+      <c r="G20" s="25" t="n">
         <v>34270</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="26" t="n">
         <v>45755</v>
       </c>
-      <c r="I20" s="21" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="n">
         <v>305</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21" t="n">
+      <c r="C21" s="22"/>
+      <c r="D21" s="22" t="n">
         <v>723701190</v>
       </c>
-      <c r="E21" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G21" s="24"/>
+      <c r="E21" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G21" s="25"/>
       <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="n">
         <v>306</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="22" t="n">
         <v>39846944</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="22" t="n">
         <v>795224557</v>
       </c>
-      <c r="E22" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F22" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="21"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
       <c r="G23" s="20"/>
       <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="n">
         <v>401</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="21" t="n">
+      <c r="C24" s="22" t="n">
         <v>29807634</v>
       </c>
-      <c r="D24" s="21" t="n">
+      <c r="D24" s="22" t="n">
         <v>703138775</v>
       </c>
-      <c r="E24" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F24" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G24" s="24"/>
+      <c r="E24" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G24" s="25"/>
       <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="n">
         <v>402</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="22" t="n">
         <v>34785180</v>
       </c>
-      <c r="D25" s="21" t="n">
+      <c r="D25" s="22" t="n">
         <v>728325855</v>
       </c>
-      <c r="E25" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
+      <c r="E25" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
       <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
         <v>403</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="22" t="n">
         <v>22248984</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="22" t="n">
         <v>718933881</v>
       </c>
-      <c r="E26" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F26" s="23" t="n">
-        <v>32000</v>
-      </c>
-      <c r="G26" s="24"/>
+      <c r="E26" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F26" s="24" t="n">
+        <v>32000</v>
+      </c>
+      <c r="G26" s="25"/>
       <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="n">
         <v>404</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="22" t="n">
         <v>34409807</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="22" t="n">
         <v>712665837</v>
       </c>
-      <c r="E27" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="21"/>
+      <c r="E27" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F27" s="24"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="22"/>
       <c r="J27" s="16" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="n">
         <v>405</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="22" t="n">
         <v>26353461</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="22" t="n">
         <v>701116277</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <v>32000</v>
       </c>
       <c r="F28" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G28" s="24"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G28" s="25" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="n">
         <v>406</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="22" t="n">
         <v>32179785</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="22" t="n">
         <v>720334200</v>
       </c>
-      <c r="E29" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="21"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E29" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
       <c r="E30" s="18"/>
       <c r="F30" s="19"/>
       <c r="G30" s="20"/>
       <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="n">
         <v>501</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="22" t="n">
         <v>797982879</v>
       </c>
-      <c r="E31" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E31" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
         <v>502</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="21" t="n">
+      <c r="C32" s="22" t="n">
         <v>328595524</v>
       </c>
-      <c r="D32" s="21" t="n">
+      <c r="D32" s="22" t="n">
         <v>798082750</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30" t="n">
+      <c r="F32" s="24"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="n">
         <v>503</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="22" t="n">
         <v>36909475</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="22" t="n">
         <v>708822190</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="23" t="n">
         <v>32000</v>
       </c>
       <c r="F33" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G33" s="24" t="n">
+      <c r="G33" s="25" t="n">
         <v>32000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>241</v>
+      </c>
+      <c r="I33" s="22" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="n">
         <v>504</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21" t="s">
+      <c r="C34" s="22"/>
+      <c r="D34" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="E34" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="21"/>
+      <c r="E34" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F34" s="32"/>
+      <c r="G34" s="25" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>243</v>
+      </c>
       <c r="J34" s="16" t="n">
         <v>450</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="n">
         <v>505</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="22" t="n">
         <v>32942992</v>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="22" t="n">
         <v>711236179</v>
       </c>
-      <c r="E35" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="24" t="n">
+      <c r="E35" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F35" s="32"/>
+      <c r="G35" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H35" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="n">
         <v>506</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="22" t="n">
         <v>30208195</v>
       </c>
-      <c r="D36" s="21" t="n">
+      <c r="D36" s="22" t="n">
         <v>708860250</v>
       </c>
-      <c r="E36" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="21"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F36" s="32"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="32"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="20"/>
       <c r="H37" s="21"/>
-      <c r="I37" s="21"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="n">
         <v>601</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="22" t="n">
         <v>31017350</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="22" t="n">
         <v>722138646</v>
       </c>
-      <c r="E38" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F38" s="31"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="21"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F38" s="32"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="n">
         <v>602</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="21" t="n">
+      <c r="B39" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" s="22" t="n">
         <v>385353317</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="22" t="n">
         <v>110147006</v>
       </c>
-      <c r="E39" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="21"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F39" s="32"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="22"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="n">
         <v>603</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="21" t="n">
+      <c r="C40" s="22" t="n">
         <v>29596759</v>
       </c>
-      <c r="D40" s="21" t="n">
+      <c r="D40" s="22" t="n">
         <v>721967235</v>
       </c>
-      <c r="E40" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="24" t="n">
+      <c r="E40" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F40" s="32"/>
+      <c r="G40" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="28" t="n">
         <v>45665</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I40" s="22" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="n">
         <v>604</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21" t="n">
+      <c r="C41" s="22"/>
+      <c r="D41" s="22" t="n">
         <v>723482227</v>
       </c>
-      <c r="E41" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="21"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F41" s="32"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="22"/>
+    </row>
+    <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="n">
         <v>605</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="C42" s="21" t="n">
+      <c r="C42" s="22" t="n">
         <v>28497464</v>
       </c>
-      <c r="D42" s="21" t="n">
+      <c r="D42" s="22" t="n">
         <v>729584979</v>
       </c>
-      <c r="E42" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F42" s="31"/>
+      <c r="E42" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F42" s="32"/>
       <c r="G42" s="20"/>
       <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I42" s="22"/>
+    </row>
+    <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="n">
         <v>606</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="22" t="n">
         <v>36635011</v>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="22" t="n">
         <v>700208592</v>
       </c>
-      <c r="E43" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F43" s="31"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="21"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F43" s="32"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="22"/>
+    </row>
+    <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
       <c r="E44" s="18"/>
-      <c r="F44" s="32"/>
+      <c r="F44" s="33"/>
       <c r="G44" s="20"/>
       <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="22"/>
+    </row>
+    <row r="45" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="n">
         <v>701</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="21" t="n">
+      <c r="C45" s="22" t="n">
         <v>36723204</v>
       </c>
-      <c r="D45" s="21" t="n">
+      <c r="D45" s="22" t="n">
         <v>743552330</v>
       </c>
-      <c r="E45" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F45" s="31"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="21"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F45" s="32"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="22"/>
+    </row>
+    <row r="46" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="n">
         <v>702</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C46" s="22" t="n">
         <v>32736219</v>
       </c>
-      <c r="D46" s="21" t="n">
+      <c r="D46" s="22" t="n">
         <v>705021087</v>
       </c>
-      <c r="E46" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="33" t="n">
+      <c r="E46" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F46" s="32"/>
+      <c r="G46" s="34" t="n">
         <v>32400</v>
       </c>
-      <c r="H46" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="I46" s="34" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="18" t="n">
         <v>703</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21" t="n">
+      <c r="C47" s="22"/>
+      <c r="D47" s="22" t="n">
         <v>717982212</v>
       </c>
-      <c r="E47" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F47" s="31"/>
-      <c r="G47" s="24" t="n">
+      <c r="E47" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F47" s="32"/>
+      <c r="G47" s="25" t="n">
         <v>35300</v>
       </c>
-      <c r="H47" s="25" t="n">
+      <c r="H47" s="26" t="n">
         <v>45665</v>
       </c>
-      <c r="I47" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I47" s="22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="18" t="n">
         <v>704</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C48" s="22" t="n">
         <v>27424733</v>
       </c>
-      <c r="D48" s="21" t="n">
+      <c r="D48" s="22" t="n">
         <v>741497042</v>
       </c>
-      <c r="E48" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="24"/>
+      <c r="E48" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F48" s="32"/>
+      <c r="G48" s="25"/>
       <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
+      <c r="I48" s="22"/>
       <c r="J48" s="16" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="18" t="n">
         <v>705</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="C49" s="21" t="n">
+      <c r="B49" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="C49" s="22" t="n">
         <v>27541354</v>
       </c>
-      <c r="D49" s="21" t="n">
+      <c r="D49" s="22" t="n">
         <v>725535858</v>
       </c>
-      <c r="E49" s="22" t="n">
+      <c r="E49" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F49" s="31"/>
-      <c r="G49" s="24" t="n">
+      <c r="F49" s="32"/>
+      <c r="G49" s="25" t="n">
         <v>31200</v>
       </c>
-      <c r="H49" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="I49" s="22" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="18" t="n">
         <v>706</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C50" s="22" t="n">
         <v>26286733</v>
       </c>
-      <c r="D50" s="21" t="n">
+      <c r="D50" s="22" t="n">
         <v>707947316</v>
       </c>
-      <c r="E50" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="24" t="n">
+      <c r="E50" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F50" s="32"/>
+      <c r="G50" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="28" t="n">
         <v>45665</v>
       </c>
-      <c r="I50" s="21" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I50" s="22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="18"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
       <c r="E51" s="18"/>
-      <c r="F51" s="32"/>
+      <c r="F51" s="33"/>
       <c r="G51" s="20"/>
       <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="22"/>
+    </row>
+    <row r="52" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="18" t="n">
         <v>801</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="21" t="n">
+      <c r="C52" s="22" t="n">
         <v>29439632</v>
       </c>
-      <c r="D52" s="21" t="n">
+      <c r="D52" s="22" t="n">
         <v>724838245</v>
       </c>
-      <c r="E52" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="21"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F52" s="32"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="22"/>
+    </row>
+    <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="n">
         <v>802</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C53" s="21" t="n">
+      <c r="C53" s="22" t="n">
         <v>32411862</v>
       </c>
-      <c r="D53" s="21" t="n">
+      <c r="D53" s="22" t="n">
         <v>720229325</v>
       </c>
-      <c r="E53" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F53" s="31"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="21"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F53" s="32"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="22"/>
+    </row>
+    <row r="54" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="18" t="n">
         <v>803</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C54" s="22" t="n">
         <v>41559757</v>
       </c>
-      <c r="D54" s="21" t="n">
+      <c r="D54" s="22" t="n">
         <v>704498777</v>
       </c>
-      <c r="E54" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="21"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F54" s="32"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="22"/>
+    </row>
+    <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="n">
         <v>804</v>
       </c>
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C55" s="21" t="n">
+      <c r="C55" s="22" t="n">
         <v>36813656</v>
       </c>
-      <c r="D55" s="21" t="n">
+      <c r="D55" s="22" t="n">
         <v>796828986</v>
       </c>
-      <c r="E55" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F55" s="31"/>
-      <c r="G55" s="24"/>
+      <c r="E55" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F55" s="32"/>
+      <c r="G55" s="25"/>
       <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I55" s="22"/>
+    </row>
+    <row r="56" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="18" t="n">
         <v>805</v>
       </c>
-      <c r="B56" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="C56" s="21" t="n">
+      <c r="B56" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C56" s="22" t="n">
         <v>25144649</v>
       </c>
-      <c r="D56" s="21" t="n">
+      <c r="D56" s="22" t="n">
         <v>726319801</v>
       </c>
-      <c r="E56" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F56" s="31"/>
-      <c r="G56" s="24" t="n">
+      <c r="E56" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F56" s="32"/>
+      <c r="G56" s="25" t="n">
         <v>35300</v>
       </c>
-      <c r="H56" s="27" t="n">
+      <c r="H56" s="28" t="n">
         <v>45696</v>
       </c>
-      <c r="I56" s="21" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I56" s="22" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="18" t="n">
         <v>806</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="C57" s="21" t="n">
+      <c r="C57" s="22" t="n">
         <v>40361306</v>
       </c>
-      <c r="D57" s="21" t="n">
+      <c r="D57" s="22" t="n">
         <v>791229029</v>
       </c>
-      <c r="E57" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F57" s="31"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="21"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F57" s="32"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="22"/>
+    </row>
+    <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
       <c r="E58" s="18"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="21"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="22"/>
       <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I58" s="22"/>
+    </row>
+    <row r="59" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="18" t="n">
         <v>901</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C59" s="21" t="n">
+      <c r="C59" s="22" t="n">
         <v>35580923</v>
       </c>
-      <c r="D59" s="21" t="n">
+      <c r="D59" s="22" t="n">
         <v>702602056</v>
       </c>
-      <c r="E59" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="25"/>
-      <c r="I59" s="21"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F59" s="32"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="22"/>
+    </row>
+    <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="18" t="n">
         <v>902</v>
       </c>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="21" t="n">
+      <c r="C60" s="22" t="n">
         <v>28068761</v>
       </c>
-      <c r="D60" s="21" t="n">
+      <c r="D60" s="22" t="n">
         <v>721178178</v>
       </c>
-      <c r="E60" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F60" s="31"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="21"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F60" s="32"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="22"/>
+    </row>
+    <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="n">
         <v>903</v>
       </c>
-      <c r="B61" s="21" t="s">
+      <c r="B61" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="21" t="n">
+      <c r="C61" s="22" t="n">
         <v>30446277</v>
       </c>
-      <c r="D61" s="21" t="s">
+      <c r="D61" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="E61" s="22" t="n">
+      <c r="E61" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F61" s="31"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="21"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F61" s="32"/>
+      <c r="G61" s="25" t="n">
+        <v>34150</v>
+      </c>
+      <c r="H61" s="26" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="18" t="n">
         <v>904</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="C62" s="21" t="n">
+      <c r="C62" s="22" t="n">
         <v>29490404</v>
       </c>
-      <c r="D62" s="21" t="n">
+      <c r="D62" s="22" t="n">
         <v>727692378</v>
       </c>
-      <c r="E62" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F62" s="31"/>
-      <c r="G62" s="30"/>
+      <c r="E62" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F62" s="32"/>
+      <c r="G62" s="31"/>
       <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I62" s="22"/>
+    </row>
+    <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
         <v>905</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21" t="n">
+      <c r="C63" s="22"/>
+      <c r="D63" s="22" t="n">
         <v>727826667</v>
       </c>
-      <c r="E63" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F63" s="31"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="21"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F63" s="32"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="22"/>
+    </row>
+    <row r="64" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="18" t="n">
         <v>906</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C64" s="21" t="n">
+      <c r="C64" s="22" t="n">
         <v>36519977</v>
       </c>
-      <c r="D64" s="21" t="n">
+      <c r="D64" s="22" t="n">
         <v>748908722</v>
       </c>
-      <c r="E64" s="22" t="n">
-        <v>32000</v>
-      </c>
-      <c r="F64" s="31"/>
-      <c r="G64" s="24"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="21"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="23" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F64" s="32"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="22"/>
+    </row>
+    <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="18"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="24"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="25"/>
       <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I65" s="22"/>
+    </row>
+    <row r="66" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C66" s="21" t="s">
+      <c r="C66" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="D66" s="21" t="n">
+      <c r="D66" s="22" t="n">
         <v>743853830</v>
       </c>
-      <c r="E66" s="22" t="n">
+      <c r="E66" s="23" t="n">
         <v>26000</v>
       </c>
-      <c r="F66" s="31"/>
-      <c r="G66" s="24" t="n">
+      <c r="F66" s="32"/>
+      <c r="G66" s="25" t="n">
         <v>29450</v>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="I66" s="21" t="s">
-        <v>253</v>
+      <c r="H66" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="18"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="21"/>
-      <c r="D67" s="21"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
       <c r="E67" s="18" t="n">
         <f aca="false">SUM(E3:E66)</f>
         <v>1685500</v>
       </c>
-      <c r="F67" s="35" t="n">
+      <c r="F67" s="37" t="n">
         <f aca="false">SUM(F3:F66)</f>
         <v>576000</v>
       </c>
-      <c r="G67" s="36" t="n">
+      <c r="G67" s="38" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>423220</v>
+        <v>625170</v>
       </c>
       <c r="H67" s="21"/>
-      <c r="I67" s="21"/>
+      <c r="I67" s="22"/>
       <c r="J67" s="16" t="n">
         <f aca="false">SUM(J3:J66)</f>
         <v>1950</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="21"/>
+    <row r="68" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="22"/>
       <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
+      <c r="I68" s="22"/>
+    </row>
+    <row r="69" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="22"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="22"/>
+      <c r="D69" s="22"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="22"/>
       <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="21"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
+      <c r="I69" s="22"/>
+    </row>
+    <row r="70" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="22"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
       <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21" t="s">
+      <c r="I70" s="22"/>
+    </row>
+    <row r="71" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="22"/>
+      <c r="B71" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="21" t="n">
+      <c r="C71" s="22" t="n">
         <v>544000</v>
       </c>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="22"/>
       <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
+      <c r="I71" s="22"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21"/>
-      <c r="B72" s="21" t="s">
+      <c r="A72" s="22"/>
+      <c r="B72" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="21" t="n">
+      <c r="C72" s="22" t="n">
         <v>1642300</v>
       </c>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
-      <c r="B73" s="21"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="22"/>
       <c r="C73" s="18" t="n">
         <f aca="false">SUM(C71:C72)</f>
         <v>2186300</v>
       </c>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
+      <c r="A74" s="22"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6140,7 +6209,7 @@
         <v>795778727</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6290,7 +6359,7 @@
         <v>728325855</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6314,7 +6383,7 @@
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>701116277</v>
@@ -6358,7 +6427,7 @@
         <v>503</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>708822190</v>
@@ -6408,7 +6477,7 @@
         <v>722138646</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6444,7 +6513,7 @@
         <v>723482227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6557,7 +6626,7 @@
         <v>720229325</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6587,7 +6656,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>726319801</v>
@@ -6670,7 +6739,7 @@
         <v>748908722</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="272">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -775,6 +775,9 @@
     <t xml:space="preserve">TH47UI0TXH </t>
   </si>
   <si>
+    <t xml:space="preserve">TH592VNB1B </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH35R3PLBD </t>
   </si>
   <si>
@@ -793,10 +796,16 @@
     <t xml:space="preserve">TGU06WRA9G</t>
   </si>
   <si>
+    <t xml:space="preserve">TH5820J7X2 </t>
+  </si>
+  <si>
     <t xml:space="preserve">ROSLYN WANGECHI CHEBET</t>
   </si>
   <si>
     <t xml:space="preserve">TGQ0K7H99S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH5810AHQE </t>
   </si>
   <si>
     <t xml:space="preserve">23/07/2025</t>
@@ -5131,9 +5140,15 @@
       <c r="F24" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="G24" s="25"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="22"/>
+      <c r="G24" s="25" t="n">
+        <v>35400</v>
+      </c>
+      <c r="H24" s="28" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="n">
@@ -5229,7 +5244,7 @@
         <v>45755</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5332,10 +5347,10 @@
         <v>32000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5360,7 +5375,7 @@
         <v>45785</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J34" s="16" t="n">
         <v>450</v>
@@ -5387,10 +5402,10 @@
         <v>32300</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5410,9 +5425,15 @@
         <v>32000</v>
       </c>
       <c r="F36" s="32"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="22"/>
+      <c r="G36" s="25" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18"/>
@@ -5451,7 +5472,7 @@
         <v>602</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>385353317</v>
@@ -5491,7 +5512,7 @@
         <v>45665</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5509,9 +5530,15 @@
         <v>32000</v>
       </c>
       <c r="F41" s="32"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="22"/>
+      <c r="G41" s="25" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H41" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I41" s="22" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="n">
@@ -5608,10 +5635,10 @@
         <v>32400</v>
       </c>
       <c r="H46" s="35" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5636,7 +5663,7 @@
         <v>45665</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5668,7 +5695,7 @@
         <v>705</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>27541354</v>
@@ -5684,10 +5711,10 @@
         <v>31200</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5714,7 +5741,7 @@
         <v>45665</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5817,7 +5844,7 @@
         <v>805</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>25144649</v>
@@ -5836,7 +5863,7 @@
         <v>45696</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5937,7 +5964,7 @@
         <v>45755</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6033,10 +6060,10 @@
         <v>29450</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6054,7 +6081,7 @@
       </c>
       <c r="G67" s="38" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>625170</v>
+        <v>731170</v>
       </c>
       <c r="H67" s="21"/>
       <c r="I67" s="22"/>
@@ -6209,7 +6236,7 @@
         <v>795778727</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6359,7 +6386,7 @@
         <v>728325855</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6383,7 +6410,7 @@
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>701116277</v>
@@ -6427,7 +6454,7 @@
         <v>503</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>708822190</v>
@@ -6477,7 +6504,7 @@
         <v>722138646</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6513,7 +6540,7 @@
         <v>723482227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6626,7 +6653,7 @@
         <v>720229325</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6656,7 +6683,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>726319801</v>
@@ -6739,7 +6766,7 @@
         <v>748908722</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="303">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -748,16 +748,56 @@
     <t xml:space="preserve">TG1959VSZV TGI65CYSWO</t>
   </si>
   <si>
-    <t xml:space="preserve">28/07/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGS4SKZSN0</t>
+    <t xml:space="preserve">INTERNET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/7/25 – 28/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGE9YQX601 – TGS4SKZSN0</t>
   </si>
   <si>
     <t xml:space="preserve">TH12I2TMAG </t>
   </si>
   <si>
-    <t xml:space="preserve">TGI0HP2QKU</t>
+    <t xml:space="preserve">18/7/25-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGI7HKOHK9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGP9HNKS29 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GINTON BROWN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/08/25 – 18/7/25</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TH18EHATI - </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Georgia"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TGI0HP2QKU</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">TH48XE8MQ0 </t>
@@ -769,18 +809,48 @@
     <t xml:space="preserve">WYCLIFFE WAFULA</t>
   </si>
   <si>
+    <t xml:space="preserve">TH88ETXKH0 </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH45XGJDCH</t>
   </si>
   <si>
+    <t xml:space="preserve">TH571VW41D </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH39OGQ5A3 </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH47UI0TXH </t>
   </si>
   <si>
+    <t xml:space="preserve">TH75DV3CY7 </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH592VNB1B </t>
   </si>
   <si>
+    <t xml:space="preserve">29/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGT715OOOJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICHOLAS GITAHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH40TGC8EG</t>
+  </si>
+  <si>
     <t xml:space="preserve">TH35R3PLBD </t>
   </si>
   <si>
+    <t xml:space="preserve">TH48XSTJRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH74DS3CQM </t>
+  </si>
+  <si>
     <t xml:space="preserve">25/07/2025</t>
   </si>
   <si>
@@ -799,15 +869,27 @@
     <t xml:space="preserve">TH5820J7X2 </t>
   </si>
   <si>
+    <t xml:space="preserve">TGT91NYS2L</t>
+  </si>
+  <si>
     <t xml:space="preserve">ROSLYN WANGECHI CHEBET</t>
   </si>
   <si>
+    <t xml:space="preserve">TH29NT36E9 </t>
+  </si>
+  <si>
     <t xml:space="preserve">TGQ0K7H99S</t>
   </si>
   <si>
     <t xml:space="preserve">TH5810AHQE </t>
   </si>
   <si>
+    <t xml:space="preserve">NV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH330WNJFP</t>
+  </si>
+  <si>
     <t xml:space="preserve">23/07/2025</t>
   </si>
   <si>
@@ -817,6 +899,12 @@
     <t xml:space="preserve">TH12EFL796 </t>
   </si>
   <si>
+    <t xml:space="preserve">26/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGQ9N4EQPR </t>
+  </si>
+  <si>
     <t xml:space="preserve">JUNIOR BEATRICE OKELO</t>
   </si>
   <si>
@@ -829,13 +917,37 @@
     <t xml:space="preserve">TH14G9MJQW</t>
   </si>
   <si>
+    <t xml:space="preserve">TH55YPXCF</t>
+  </si>
+  <si>
     <t xml:space="preserve">TIMOTHY MUCHERU</t>
   </si>
   <si>
     <t xml:space="preserve">TH26J2JUU6 </t>
   </si>
   <si>
+    <t xml:space="preserve">31/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGV8B1BY92 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH10F9V1JU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH521KIEAE </t>
+  </si>
+  <si>
     <t xml:space="preserve">TH44V0HDVC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH15GNK5N3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TH70E5IAB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOHAMED SHARIF</t>
   </si>
   <si>
     <t xml:space="preserve">31/7/2025</t>
@@ -1104,7 +1216,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1219,6 +1331,10 @@
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -4601,7 +4717,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="13.12"/>
@@ -4614,7 +4730,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="21.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="33.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="16" width="21.11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="16" width="8.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="25.48"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="16" width="8.54"/>
   </cols>
   <sheetData>
     <row r="1" s="17" customFormat="true" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4651,6 +4768,9 @@
         <v>8</v>
       </c>
       <c r="J2" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="K2" s="18" t="s">
         <v>143</v>
       </c>
     </row>
@@ -4677,10 +4797,10 @@
         <v>32000</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4707,7 +4827,7 @@
         <v>45665</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4718,12 +4838,18 @@
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
       <c r="E5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="24"/>
+        <v>32000</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>32000</v>
+      </c>
       <c r="G5" s="20"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
+      <c r="H5" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="n">
@@ -4744,15 +4870,23 @@
       <c r="F6" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="22"/>
+      <c r="G6" s="20" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="n">
         <v>105</v>
       </c>
-      <c r="B7" s="22"/>
+      <c r="B7" s="22" t="s">
+        <v>239</v>
+      </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22"/>
       <c r="E7" s="18" t="n">
@@ -4764,11 +4898,11 @@
       <c r="G7" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="H7" s="28" t="n">
-        <v>45665</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>234</v>
+      <c r="H7" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4797,7 +4931,7 @@
         <v>45755</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4853,22 +4987,22 @@
       <c r="F11" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G11" s="29" t="n">
+      <c r="G11" s="30" t="n">
         <v>32300</v>
       </c>
       <c r="H11" s="26" t="n">
         <v>45696</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="n">
         <v>203</v>
       </c>
-      <c r="B12" s="30" t="s">
-        <v>237</v>
+      <c r="B12" s="31" t="s">
+        <v>244</v>
       </c>
       <c r="C12" s="22" t="n">
         <v>26743529</v>
@@ -4905,7 +5039,9 @@
       <c r="F13" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="25" t="n">
+        <v>32000</v>
+      </c>
       <c r="H13" s="21"/>
       <c r="I13" s="22"/>
     </row>
@@ -4920,7 +5056,7 @@
         <v>162</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>7417077875</v>
+        <v>741707875</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>32000</v>
@@ -4928,9 +5064,15 @@
       <c r="F14" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="22"/>
+      <c r="G14" s="25" t="n">
+        <v>35600</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>45877</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="n">
@@ -4992,7 +5134,7 @@
         <v>45755</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5012,9 +5154,15 @@
         <v>32000</v>
       </c>
       <c r="F18" s="24"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="22"/>
+      <c r="G18" s="25" t="n">
+        <v>35600</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I18" s="22" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="n">
@@ -5035,9 +5183,18 @@
       <c r="F19" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="22"/>
+      <c r="G19" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>45724</v>
+      </c>
+      <c r="I19" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="18" t="n">
@@ -5063,7 +5220,7 @@
         <v>45755</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5083,9 +5240,15 @@
       <c r="F21" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="22"/>
+      <c r="G21" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H21" s="28" t="n">
+        <v>45696</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="n">
@@ -5147,7 +5310,7 @@
         <v>45785</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5167,16 +5330,25 @@
         <v>32000</v>
       </c>
       <c r="F25" s="24"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="22"/>
+      <c r="G25" s="25" t="n">
+        <v>31500</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="I25" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="J25" s="16" t="n">
+        <v>3500</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="n">
         <v>403</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="C26" s="22" t="n">
         <v>22248984</v>
@@ -5190,9 +5362,15 @@
       <c r="F26" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="22"/>
+      <c r="G26" s="25" t="n">
+        <v>32150</v>
+      </c>
+      <c r="H26" s="28" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I26" s="22" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="n">
@@ -5214,7 +5392,7 @@
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
       <c r="I27" s="22"/>
-      <c r="J27" s="16" t="n">
+      <c r="K27" s="16" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5244,7 +5422,7 @@
         <v>45755</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5296,9 +5474,15 @@
         <v>32000</v>
       </c>
       <c r="F31" s="24"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="22"/>
+      <c r="G31" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H31" s="26" t="n">
+        <v>45755</v>
+      </c>
+      <c r="I31" s="22" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="n">
@@ -5317,10 +5501,17 @@
         <v>30500</v>
       </c>
       <c r="F32" s="24"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31" t="n">
+      <c r="G32" s="25" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>45846</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5347,10 +5538,10 @@
         <v>32000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5361,13 +5552,13 @@
         <v>47</v>
       </c>
       <c r="C34" s="22"/>
-      <c r="D34" s="22" t="s">
-        <v>136</v>
+      <c r="D34" s="22" t="n">
+        <v>718169400</v>
       </c>
       <c r="E34" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F34" s="32"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5375,9 +5566,9 @@
         <v>45785</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="J34" s="16" t="n">
+        <v>261</v>
+      </c>
+      <c r="K34" s="16" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5397,15 +5588,15 @@
       <c r="E35" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F35" s="32"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="25" t="n">
         <v>32300</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5424,7 +5615,7 @@
       <c r="E36" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F36" s="32"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5432,7 +5623,7 @@
         <v>45785</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5441,7 +5632,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="33"/>
+      <c r="F37" s="34"/>
       <c r="G37" s="20"/>
       <c r="H37" s="21"/>
       <c r="I37" s="22"/>
@@ -5462,17 +5653,23 @@
       <c r="E38" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F38" s="32"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="22"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="25" t="n">
+        <v>32750</v>
+      </c>
+      <c r="H38" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="n">
         <v>602</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>385353317</v>
@@ -5483,10 +5680,16 @@
       <c r="E39" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F39" s="32"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="22"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>45696</v>
+      </c>
+      <c r="I39" s="22" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="n">
@@ -5504,7 +5707,7 @@
       <c r="E40" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F40" s="32"/>
+      <c r="F40" s="33"/>
       <c r="G40" s="25" t="n">
         <v>32300</v>
       </c>
@@ -5512,7 +5715,7 @@
         <v>45665</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5529,7 +5732,7 @@
       <c r="E41" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F41" s="32"/>
+      <c r="F41" s="33"/>
       <c r="G41" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5537,7 +5740,7 @@
         <v>45785</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5556,10 +5759,16 @@
       <c r="E42" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F42" s="32"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="22"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="20" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="I42" s="22" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="18" t="n">
@@ -5577,10 +5786,16 @@
       <c r="E43" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F43" s="32"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="22"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="25" t="n">
+        <v>32150</v>
+      </c>
+      <c r="H43" s="26" t="n">
+        <v>45724</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="18"/>
@@ -5588,7 +5803,7 @@
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
       <c r="E44" s="18"/>
-      <c r="F44" s="33"/>
+      <c r="F44" s="34"/>
       <c r="G44" s="20"/>
       <c r="H44" s="21"/>
       <c r="I44" s="22"/>
@@ -5609,7 +5824,7 @@
       <c r="E45" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F45" s="32"/>
+      <c r="F45" s="33"/>
       <c r="G45" s="25"/>
       <c r="H45" s="26"/>
       <c r="I45" s="22"/>
@@ -5630,15 +5845,15 @@
       <c r="E46" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F46" s="32"/>
-      <c r="G46" s="34" t="n">
+      <c r="F46" s="33"/>
+      <c r="G46" s="35" t="n">
         <v>32400</v>
       </c>
-      <c r="H46" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="I46" s="36" t="s">
-        <v>252</v>
+      <c r="H46" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5655,7 +5870,7 @@
       <c r="E47" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F47" s="32"/>
+      <c r="F47" s="33"/>
       <c r="G47" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5663,7 +5878,7 @@
         <v>45665</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5682,11 +5897,17 @@
       <c r="E48" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F48" s="32"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="16" t="n">
+      <c r="F48" s="33"/>
+      <c r="G48" s="25" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K48" s="16" t="n">
         <v>600</v>
       </c>
     </row>
@@ -5695,7 +5916,7 @@
         <v>705</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>27541354</v>
@@ -5706,15 +5927,15 @@
       <c r="E49" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F49" s="32"/>
+      <c r="F49" s="33"/>
       <c r="G49" s="25" t="n">
         <v>31200</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5733,7 +5954,7 @@
       <c r="E50" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F50" s="32"/>
+      <c r="F50" s="33"/>
       <c r="G50" s="25" t="n">
         <v>32400</v>
       </c>
@@ -5741,7 +5962,7 @@
         <v>45665</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5750,7 +5971,7 @@
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
       <c r="E51" s="18"/>
-      <c r="F51" s="33"/>
+      <c r="F51" s="34"/>
       <c r="G51" s="20"/>
       <c r="H51" s="21"/>
       <c r="I51" s="22"/>
@@ -5771,8 +5992,8 @@
       <c r="E52" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F52" s="32"/>
-      <c r="G52" s="29"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="30"/>
       <c r="H52" s="26"/>
       <c r="I52" s="22"/>
     </row>
@@ -5792,7 +6013,7 @@
       <c r="E53" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F53" s="32"/>
+      <c r="F53" s="33"/>
       <c r="G53" s="25"/>
       <c r="H53" s="26"/>
       <c r="I53" s="22"/>
@@ -5813,10 +6034,16 @@
       <c r="E54" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F54" s="32"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="22"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="25" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H54" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I54" s="22" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="n">
@@ -5834,7 +6061,7 @@
       <c r="E55" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F55" s="32"/>
+      <c r="F55" s="33"/>
       <c r="G55" s="25"/>
       <c r="H55" s="21"/>
       <c r="I55" s="22"/>
@@ -5844,7 +6071,7 @@
         <v>805</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>25144649</v>
@@ -5855,7 +6082,7 @@
       <c r="E56" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F56" s="32"/>
+      <c r="F56" s="33"/>
       <c r="G56" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5863,7 +6090,7 @@
         <v>45696</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5882,10 +6109,16 @@
       <c r="E57" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F57" s="32"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="22"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="25" t="n">
+        <v>35300</v>
+      </c>
+      <c r="H57" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="I57" s="22" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="18"/>
@@ -5893,7 +6126,7 @@
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
       <c r="E58" s="18"/>
-      <c r="F58" s="33"/>
+      <c r="F58" s="34"/>
       <c r="G58" s="22"/>
       <c r="H58" s="21"/>
       <c r="I58" s="22"/>
@@ -5914,10 +6147,16 @@
       <c r="E59" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F59" s="32"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="22"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="25" t="n">
+        <v>32450</v>
+      </c>
+      <c r="H59" s="26" t="n">
+        <v>45665</v>
+      </c>
+      <c r="I59" s="22" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="18" t="n">
@@ -5935,10 +6174,16 @@
       <c r="E60" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F60" s="32"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="22"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H60" s="26" t="n">
+        <v>45785</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="18" t="n">
@@ -5956,7 +6201,7 @@
       <c r="E61" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F61" s="32"/>
+      <c r="F61" s="33"/>
       <c r="G61" s="25" t="n">
         <v>34150</v>
       </c>
@@ -5964,7 +6209,7 @@
         <v>45755</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5983,10 +6228,16 @@
       <c r="E62" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F62" s="32"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="22"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="25" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H62" s="28" t="n">
+        <v>45665</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="18" t="n">
@@ -6002,8 +6253,8 @@
       <c r="E63" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F63" s="32"/>
-      <c r="G63" s="31"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="32"/>
       <c r="H63" s="26"/>
       <c r="I63" s="22"/>
     </row>
@@ -6023,10 +6274,16 @@
       <c r="E64" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F64" s="32"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="22"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="25" t="n">
+        <v>35450</v>
+      </c>
+      <c r="H64" s="26" t="n">
+        <v>45846</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="18"/>
@@ -6034,7 +6291,7 @@
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
       <c r="E65" s="23"/>
-      <c r="F65" s="32"/>
+      <c r="F65" s="33"/>
       <c r="G65" s="25"/>
       <c r="H65" s="21"/>
       <c r="I65" s="22"/>
@@ -6044,7 +6301,7 @@
         <v>126</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="C66" s="22" t="s">
         <v>229</v>
@@ -6055,15 +6312,15 @@
       <c r="E66" s="23" t="n">
         <v>26000</v>
       </c>
-      <c r="F66" s="32"/>
+      <c r="F66" s="33"/>
       <c r="G66" s="25" t="n">
         <v>29450</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6073,20 +6330,24 @@
       <c r="D67" s="22"/>
       <c r="E67" s="18" t="n">
         <f aca="false">SUM(E3:E66)</f>
-        <v>1685500</v>
-      </c>
-      <c r="F67" s="37" t="n">
+        <v>1717500</v>
+      </c>
+      <c r="F67" s="38" t="n">
         <f aca="false">SUM(F3:F66)</f>
-        <v>576000</v>
-      </c>
-      <c r="G67" s="38" t="n">
+        <v>608000</v>
+      </c>
+      <c r="G67" s="39" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>731170</v>
+        <v>1426220</v>
       </c>
       <c r="H67" s="21"/>
       <c r="I67" s="22"/>
       <c r="J67" s="16" t="n">
         <f aca="false">SUM(J3:J66)</f>
+        <v>6500</v>
+      </c>
+      <c r="K67" s="16" t="n">
+        <f aca="false">SUM(K3:K66)</f>
         <v>1950</v>
       </c>
     </row>
@@ -6096,7 +6357,7 @@
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="32"/>
+      <c r="F68" s="33"/>
       <c r="G68" s="22"/>
       <c r="H68" s="21"/>
       <c r="I68" s="22"/>
@@ -6148,7 +6409,7 @@
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
-      <c r="F72" s="31"/>
+      <c r="F72" s="32"/>
       <c r="G72" s="22"/>
       <c r="H72" s="22"/>
       <c r="I72" s="22"/>
@@ -6236,7 +6497,7 @@
         <v>795778727</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6386,7 +6647,7 @@
         <v>728325855</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6410,7 +6671,7 @@
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>701116277</v>
@@ -6454,7 +6715,7 @@
         <v>503</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>708822190</v>
@@ -6504,7 +6765,7 @@
         <v>722138646</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6540,7 +6801,7 @@
         <v>723482227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6653,7 +6914,7 @@
         <v>720229325</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6683,7 +6944,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>726319801</v>
@@ -6766,7 +7027,7 @@
         <v>748908722</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="306">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -890,6 +890,9 @@
     <t xml:space="preserve">TH330WNJFP</t>
   </si>
   <si>
+    <t xml:space="preserve">TG37FU30C3</t>
+  </si>
+  <si>
     <t xml:space="preserve">23/07/2025</t>
   </si>
   <si>
@@ -915,6 +918,12 @@
   </si>
   <si>
     <t xml:space="preserve">TH14G9MJQW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/07/25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGO7AONY1Z </t>
   </si>
   <si>
     <t xml:space="preserve">TH55YPXCF</t>
@@ -1216,7 +1225,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1327,6 +1336,10 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -4717,7 +4730,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="13.12"/>
@@ -4835,7 +4848,7 @@
         <v>103</v>
       </c>
       <c r="B5" s="27"/>
-      <c r="C5" s="22"/>
+      <c r="C5" s="28"/>
       <c r="D5" s="22"/>
       <c r="E5" s="18" t="n">
         <v>32000</v>
@@ -4858,7 +4871,7 @@
       <c r="B6" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="28" t="n">
         <v>22203283</v>
       </c>
       <c r="D6" s="22" t="n">
@@ -4887,7 +4900,7 @@
       <c r="B7" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="28"/>
       <c r="D7" s="22"/>
       <c r="E7" s="18" t="n">
         <v>32000</v>
@@ -4898,10 +4911,10 @@
       <c r="G7" s="20" t="n">
         <v>32000</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4912,7 +4925,7 @@
       <c r="B8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="28" t="n">
         <v>26007698</v>
       </c>
       <c r="D8" s="22" t="n">
@@ -4927,7 +4940,7 @@
       <c r="G8" s="25" t="n">
         <v>32600</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="29" t="n">
         <v>45755</v>
       </c>
       <c r="I8" s="22" t="s">
@@ -4937,7 +4950,7 @@
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18"/>
       <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="22"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
@@ -4952,7 +4965,7 @@
       <c r="B10" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="28" t="n">
         <v>28689105</v>
       </c>
       <c r="D10" s="22" t="n">
@@ -4975,7 +4988,7 @@
       <c r="B11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="28" t="n">
         <v>34497236</v>
       </c>
       <c r="D11" s="22" t="n">
@@ -4987,7 +5000,7 @@
       <c r="F11" s="19" t="n">
         <v>32000</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="31" t="n">
         <v>32300</v>
       </c>
       <c r="H11" s="26" t="n">
@@ -5001,10 +5014,10 @@
       <c r="A12" s="18" t="n">
         <v>203</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="28" t="n">
         <v>26743529</v>
       </c>
       <c r="D12" s="22" t="n">
@@ -5027,7 +5040,7 @@
       <c r="B13" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="28" t="n">
         <v>37925531</v>
       </c>
       <c r="D13" s="22" t="n">
@@ -5052,7 +5065,7 @@
       <c r="B14" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="28" t="s">
         <v>162</v>
       </c>
       <c r="D14" s="22" t="n">
@@ -5067,7 +5080,7 @@
       <c r="G14" s="25" t="n">
         <v>35600</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="29" t="n">
         <v>45877</v>
       </c>
       <c r="I14" s="22" t="s">
@@ -5081,7 +5094,7 @@
       <c r="B15" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="28" t="n">
         <v>23406138</v>
       </c>
       <c r="D15" s="22" t="n">
@@ -5100,7 +5113,7 @@
     <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="18"/>
       <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
+      <c r="C16" s="28"/>
       <c r="D16" s="22"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19"/>
@@ -5115,7 +5128,7 @@
       <c r="B17" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="28" t="n">
         <v>32437159</v>
       </c>
       <c r="D17" s="22" t="n">
@@ -5130,7 +5143,7 @@
       <c r="G17" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="29" t="n">
         <v>45755</v>
       </c>
       <c r="I17" s="22" t="s">
@@ -5144,7 +5157,7 @@
       <c r="B18" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C18" s="28" t="n">
         <v>25074051</v>
       </c>
       <c r="D18" s="22" t="n">
@@ -5171,7 +5184,7 @@
       <c r="B19" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="28" t="n">
         <v>28508205</v>
       </c>
       <c r="D19" s="22" t="n">
@@ -5203,7 +5216,7 @@
       <c r="B20" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C20" s="28" t="n">
         <v>672131885</v>
       </c>
       <c r="D20" s="22" t="n">
@@ -5230,7 +5243,7 @@
       <c r="B21" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="28"/>
       <c r="D21" s="22" t="n">
         <v>723701190</v>
       </c>
@@ -5243,7 +5256,7 @@
       <c r="G21" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="29" t="n">
         <v>45696</v>
       </c>
       <c r="I21" s="22" t="s">
@@ -5257,7 +5270,7 @@
       <c r="B22" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C22" s="28" t="n">
         <v>39846944</v>
       </c>
       <c r="D22" s="22" t="n">
@@ -5276,7 +5289,7 @@
     <row r="23" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18"/>
       <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="22"/>
       <c r="E23" s="18"/>
       <c r="F23" s="19"/>
@@ -5291,7 +5304,7 @@
       <c r="B24" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="22" t="n">
+      <c r="C24" s="28" t="n">
         <v>29807634</v>
       </c>
       <c r="D24" s="22" t="n">
@@ -5306,7 +5319,7 @@
       <c r="G24" s="25" t="n">
         <v>35400</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="29" t="n">
         <v>45785</v>
       </c>
       <c r="I24" s="22" t="s">
@@ -5320,7 +5333,7 @@
       <c r="B25" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="28" t="n">
         <v>34785180</v>
       </c>
       <c r="D25" s="22" t="n">
@@ -5350,7 +5363,7 @@
       <c r="B26" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="C26" s="22" t="n">
+      <c r="C26" s="28" t="n">
         <v>22248984</v>
       </c>
       <c r="D26" s="22" t="n">
@@ -5365,7 +5378,7 @@
       <c r="G26" s="25" t="n">
         <v>32150</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="29" t="n">
         <v>45755</v>
       </c>
       <c r="I26" s="22" t="s">
@@ -5379,7 +5392,7 @@
       <c r="B27" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="28" t="n">
         <v>34409807</v>
       </c>
       <c r="D27" s="22" t="n">
@@ -5403,7 +5416,7 @@
       <c r="B28" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="C28" s="22" t="n">
+      <c r="C28" s="28" t="n">
         <v>26353461</v>
       </c>
       <c r="D28" s="22" t="n">
@@ -5418,7 +5431,7 @@
       <c r="G28" s="25" t="n">
         <v>35300</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="29" t="n">
         <v>45755</v>
       </c>
       <c r="I28" s="22" t="s">
@@ -5432,7 +5445,7 @@
       <c r="B29" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="28" t="n">
         <v>32179785</v>
       </c>
       <c r="D29" s="22" t="n">
@@ -5449,7 +5462,7 @@
     <row r="30" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18"/>
       <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
+      <c r="C30" s="28"/>
       <c r="D30" s="22"/>
       <c r="E30" s="18"/>
       <c r="F30" s="19"/>
@@ -5464,7 +5477,7 @@
       <c r="B31" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="28" t="s">
         <v>192</v>
       </c>
       <c r="D31" s="22" t="n">
@@ -5491,7 +5504,7 @@
       <c r="B32" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="28" t="n">
         <v>328595524</v>
       </c>
       <c r="D32" s="22" t="n">
@@ -5507,11 +5520,11 @@
       <c r="H32" s="26" t="n">
         <v>45846</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32" t="n">
+      <c r="J32" s="33"/>
+      <c r="K32" s="33" t="n">
         <v>450</v>
       </c>
     </row>
@@ -5558,7 +5571,7 @@
       <c r="E34" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F34" s="33"/>
+      <c r="F34" s="34"/>
       <c r="G34" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5588,7 +5601,7 @@
       <c r="E35" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F35" s="33"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="25" t="n">
         <v>32300</v>
       </c>
@@ -5615,7 +5628,7 @@
       <c r="E36" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F36" s="33"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5632,7 +5645,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
       <c r="E37" s="18"/>
-      <c r="F37" s="34"/>
+      <c r="F37" s="35"/>
       <c r="G37" s="20"/>
       <c r="H37" s="21"/>
       <c r="I37" s="22"/>
@@ -5653,7 +5666,7 @@
       <c r="E38" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F38" s="33"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="25" t="n">
         <v>32750</v>
       </c>
@@ -5680,7 +5693,7 @@
       <c r="E39" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F39" s="33"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="25" t="n">
         <v>32300</v>
       </c>
@@ -5707,11 +5720,11 @@
       <c r="E40" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F40" s="33"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H40" s="28" t="n">
+      <c r="H40" s="29" t="n">
         <v>45665</v>
       </c>
       <c r="I40" s="22" t="s">
@@ -5732,7 +5745,7 @@
       <c r="E41" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F41" s="33"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5759,7 +5772,7 @@
       <c r="E42" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F42" s="33"/>
+      <c r="F42" s="34"/>
       <c r="G42" s="20" t="n">
         <v>35300</v>
       </c>
@@ -5786,7 +5799,7 @@
       <c r="E43" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F43" s="33"/>
+      <c r="F43" s="34"/>
       <c r="G43" s="25" t="n">
         <v>32150</v>
       </c>
@@ -5803,7 +5816,7 @@
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
       <c r="E44" s="18"/>
-      <c r="F44" s="34"/>
+      <c r="F44" s="35"/>
       <c r="G44" s="20"/>
       <c r="H44" s="21"/>
       <c r="I44" s="22"/>
@@ -5824,10 +5837,16 @@
       <c r="E45" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F45" s="33"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="22"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="25" t="n">
+        <v>35900</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>45723</v>
+      </c>
+      <c r="I45" s="22" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="18" t="n">
@@ -5845,15 +5864,15 @@
       <c r="E46" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F46" s="33"/>
-      <c r="G46" s="35" t="n">
+      <c r="F46" s="34"/>
+      <c r="G46" s="36" t="n">
         <v>32400</v>
       </c>
-      <c r="H46" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="I46" s="37" t="s">
+      <c r="H46" s="37" t="s">
         <v>273</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,7 +5889,7 @@
       <c r="E47" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F47" s="33"/>
+      <c r="F47" s="34"/>
       <c r="G47" s="25" t="n">
         <v>35300</v>
       </c>
@@ -5878,7 +5897,7 @@
         <v>45665</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5897,15 +5916,15 @@
       <c r="E48" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F48" s="33"/>
+      <c r="F48" s="34"/>
       <c r="G48" s="25" t="n">
         <v>32000</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="I48" s="37" t="s">
         <v>276</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>277</v>
       </c>
       <c r="K48" s="16" t="n">
         <v>600</v>
@@ -5916,7 +5935,7 @@
         <v>705</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>27541354</v>
@@ -5927,15 +5946,15 @@
       <c r="E49" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F49" s="33"/>
+      <c r="F49" s="34"/>
       <c r="G49" s="25" t="n">
         <v>31200</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5954,15 +5973,15 @@
       <c r="E50" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F50" s="33"/>
+      <c r="F50" s="34"/>
       <c r="G50" s="25" t="n">
         <v>32400</v>
       </c>
-      <c r="H50" s="28" t="n">
+      <c r="H50" s="29" t="n">
         <v>45665</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5971,7 +5990,7 @@
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
       <c r="E51" s="18"/>
-      <c r="F51" s="34"/>
+      <c r="F51" s="35"/>
       <c r="G51" s="20"/>
       <c r="H51" s="21"/>
       <c r="I51" s="22"/>
@@ -5992,10 +6011,19 @@
       <c r="E52" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F52" s="33"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="22"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="31" t="n">
+        <v>32300</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="L52" s="16" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="18" t="n">
@@ -6013,7 +6041,7 @@
       <c r="E53" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F53" s="33"/>
+      <c r="F53" s="34"/>
       <c r="G53" s="25"/>
       <c r="H53" s="26"/>
       <c r="I53" s="22"/>
@@ -6034,7 +6062,7 @@
       <c r="E54" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F54" s="33"/>
+      <c r="F54" s="34"/>
       <c r="G54" s="25" t="n">
         <v>35000</v>
       </c>
@@ -6042,7 +6070,7 @@
         <v>45785</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6061,7 +6089,7 @@
       <c r="E55" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F55" s="33"/>
+      <c r="F55" s="34"/>
       <c r="G55" s="25"/>
       <c r="H55" s="21"/>
       <c r="I55" s="22"/>
@@ -6071,7 +6099,7 @@
         <v>805</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>25144649</v>
@@ -6082,15 +6110,15 @@
       <c r="E56" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F56" s="33"/>
+      <c r="F56" s="34"/>
       <c r="G56" s="25" t="n">
         <v>35300</v>
       </c>
-      <c r="H56" s="28" t="n">
+      <c r="H56" s="29" t="n">
         <v>45696</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6109,15 +6137,15 @@
       <c r="E57" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F57" s="33"/>
+      <c r="F57" s="34"/>
       <c r="G57" s="25" t="n">
         <v>35300</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6126,7 +6154,7 @@
       <c r="C58" s="22"/>
       <c r="D58" s="22"/>
       <c r="E58" s="18"/>
-      <c r="F58" s="34"/>
+      <c r="F58" s="35"/>
       <c r="G58" s="22"/>
       <c r="H58" s="21"/>
       <c r="I58" s="22"/>
@@ -6147,7 +6175,7 @@
       <c r="E59" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F59" s="33"/>
+      <c r="F59" s="34"/>
       <c r="G59" s="25" t="n">
         <v>32450</v>
       </c>
@@ -6155,7 +6183,7 @@
         <v>45665</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6174,7 +6202,7 @@
       <c r="E60" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F60" s="33"/>
+      <c r="F60" s="34"/>
       <c r="G60" s="25" t="n">
         <v>32300</v>
       </c>
@@ -6182,7 +6210,7 @@
         <v>45785</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6201,7 +6229,7 @@
       <c r="E61" s="23" t="n">
         <v>30500</v>
       </c>
-      <c r="F61" s="33"/>
+      <c r="F61" s="34"/>
       <c r="G61" s="25" t="n">
         <v>34150</v>
       </c>
@@ -6209,7 +6237,7 @@
         <v>45755</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6228,15 +6256,15 @@
       <c r="E62" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F62" s="33"/>
+      <c r="F62" s="34"/>
       <c r="G62" s="25" t="n">
         <v>32300</v>
       </c>
-      <c r="H62" s="28" t="n">
+      <c r="H62" s="29" t="n">
         <v>45665</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6253,8 +6281,8 @@
       <c r="E63" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F63" s="33"/>
-      <c r="G63" s="32"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="33"/>
       <c r="H63" s="26"/>
       <c r="I63" s="22"/>
     </row>
@@ -6274,7 +6302,7 @@
       <c r="E64" s="23" t="n">
         <v>32000</v>
       </c>
-      <c r="F64" s="33"/>
+      <c r="F64" s="34"/>
       <c r="G64" s="25" t="n">
         <v>35450</v>
       </c>
@@ -6282,7 +6310,7 @@
         <v>45846</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,7 +6319,7 @@
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
       <c r="E65" s="23"/>
-      <c r="F65" s="33"/>
+      <c r="F65" s="34"/>
       <c r="G65" s="25"/>
       <c r="H65" s="21"/>
       <c r="I65" s="22"/>
@@ -6301,7 +6329,7 @@
         <v>126</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C66" s="22" t="s">
         <v>229</v>
@@ -6312,15 +6340,15 @@
       <c r="E66" s="23" t="n">
         <v>26000</v>
       </c>
-      <c r="F66" s="33"/>
+      <c r="F66" s="34"/>
       <c r="G66" s="25" t="n">
         <v>29450</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6332,13 +6360,13 @@
         <f aca="false">SUM(E3:E66)</f>
         <v>1717500</v>
       </c>
-      <c r="F67" s="38" t="n">
+      <c r="F67" s="39" t="n">
         <f aca="false">SUM(F3:F66)</f>
         <v>608000</v>
       </c>
-      <c r="G67" s="39" t="n">
+      <c r="G67" s="40" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>1426220</v>
+        <v>1494420</v>
       </c>
       <c r="H67" s="21"/>
       <c r="I67" s="22"/>
@@ -6357,7 +6385,7 @@
       <c r="C68" s="22"/>
       <c r="D68" s="22"/>
       <c r="E68" s="22"/>
-      <c r="F68" s="33"/>
+      <c r="F68" s="34"/>
       <c r="G68" s="22"/>
       <c r="H68" s="21"/>
       <c r="I68" s="22"/>
@@ -6409,7 +6437,7 @@
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
-      <c r="F72" s="32"/>
+      <c r="F72" s="33"/>
       <c r="G72" s="22"/>
       <c r="H72" s="22"/>
       <c r="I72" s="22"/>
@@ -6497,7 +6525,7 @@
         <v>795778727</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6647,7 +6675,7 @@
         <v>728325855</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6671,7 +6699,7 @@
         <v>405</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>701116277</v>
@@ -6715,7 +6743,7 @@
         <v>503</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>708822190</v>
@@ -6765,7 +6793,7 @@
         <v>722138646</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6801,7 +6829,7 @@
         <v>723482227</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6914,7 +6942,7 @@
         <v>720229325</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6944,7 +6972,7 @@
         <v>805</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>726319801</v>
@@ -7027,7 +7055,7 @@
         <v>748908722</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
+++ b/PROPERTIES/NJENY HEIGHTS/NJENY APARTMENTS PAYMENT UPDATES .xlsx
@@ -12,7 +12,6 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="JULY" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="AUG" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="299">
   <si>
     <t xml:space="preserve">                         NJENY APARTMENTS PAYMENT DETAILS</t>
   </si>
@@ -760,6 +759,12 @@
     <t xml:space="preserve">TH12I2TMAG </t>
   </si>
   <si>
+    <t xml:space="preserve">WILLIE CINDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A60141226</t>
+  </si>
+  <si>
     <t xml:space="preserve">18/7/25-</t>
   </si>
   <si>
@@ -963,33 +968,6 @@
   </si>
   <si>
     <t xml:space="preserve">TGV8CFF4VQ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">61,000 PAID BY FAITH NEEMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,000 PAID BY KEVIN MAYWAKA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHRISTINE NJERI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MICHAEL KWIZERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15,000 PAID BY CAROLYN CHEPKEMOI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,000 PAID BY CHARLES N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STANLEY AGESA 32,000 BRENDA MKANDOE 32,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,000 PAID BY CATHERINE ESTHER NYAMBURA</t>
   </si>
 </sst>
 </file>
@@ -4847,8 +4825,12 @@
       <c r="A5" s="18" t="n">
         <v>103</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
+      <c r="B5" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="D5" s="22"/>
       <c r="E5" s="18" t="n">
         <v>32000</v>
@@ -4856,12 +4838,14 @@
       <c r="F5" s="24" t="n">
         <v>32000</v>
       </c>
-      <c r="G5" s="20"/>
+      <c r="G5" s="20" t="n">
+        <v>40000</v>
+      </c>
       <c r="H5" s="21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4887,10 +4871,10 @@
         <v>32000</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4898,7 +4882,7 @@
         <v>105</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="22"/>
@@ -4912,10 +4896,10 @@
         <v>32000</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4944,7 +4928,7 @@
         <v>45755</v>
       </c>
       <c r="I8" s="22" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5007,7 +4991,7 @@
         <v>45696</v>
       </c>
       <c r="I11" s="22" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5015,7 +4999,7 @@
         <v>203</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C12" s="28" t="n">
         <v>26743529</v>
@@ -5084,7 +5068,7 @@
         <v>45877</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5147,7 +5131,7 @@
         <v>45755</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5174,7 +5158,7 @@
         <v>45785</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5203,7 +5187,7 @@
         <v>45724</v>
       </c>
       <c r="I19" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J19" s="16" t="n">
         <v>3000</v>
@@ -5233,7 +5217,7 @@
         <v>45755</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5260,7 +5244,7 @@
         <v>45696</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,7 +5307,7 @@
         <v>45785</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5347,10 +5331,10 @@
         <v>31500</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I25" s="22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J25" s="16" t="n">
         <v>3500</v>
@@ -5361,7 +5345,7 @@
         <v>403</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C26" s="28" t="n">
         <v>22248984</v>
@@ -5382,7 +5366,7 @@
         <v>45755</v>
       </c>
       <c r="I26" s="22" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5435,7 +5419,7 @@
         <v>45755</v>
       </c>
       <c r="I28" s="22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,7 +5478,7 @@
         <v>45755</v>
       </c>
       <c r="I31" s="22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,7 +5505,7 @@
         <v>45846</v>
       </c>
       <c r="I32" s="33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J32" s="33"/>
       <c r="K32" s="33" t="n">
@@ -5551,10 +5535,10 @@
         <v>32000</v>
       </c>
       <c r="H33" s="21" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I33" s="22" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5579,7 +5563,7 @@
         <v>45785</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K34" s="16" t="n">
         <v>450</v>
@@ -5606,10 +5590,10 @@
         <v>32300</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I35" s="22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5636,7 +5620,7 @@
         <v>45785</v>
       </c>
       <c r="I36" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5671,10 +5655,10 @@
         <v>32750</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I38" s="22" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5682,7 +5666,7 @@
         <v>602</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C39" s="22" t="n">
         <v>385353317</v>
@@ -5701,7 +5685,7 @@
         <v>45696</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5728,7 +5712,7 @@
         <v>45665</v>
       </c>
       <c r="I40" s="22" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5753,7 +5737,7 @@
         <v>45785</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5777,10 +5761,10 @@
         <v>35300</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I42" s="22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5807,7 +5791,7 @@
         <v>45724</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5845,7 +5829,7 @@
         <v>45723</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,10 +5853,10 @@
         <v>32400</v>
       </c>
       <c r="H46" s="37" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5897,7 +5881,7 @@
         <v>45665</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,10 +5905,10 @@
         <v>32000</v>
       </c>
       <c r="H48" s="21" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K48" s="16" t="n">
         <v>600</v>
@@ -5935,7 +5919,7 @@
         <v>705</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C49" s="22" t="n">
         <v>27541354</v>
@@ -5951,10 +5935,10 @@
         <v>31200</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5981,7 +5965,7 @@
         <v>45665</v>
       </c>
       <c r="I50" s="22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6016,10 +6000,10 @@
         <v>32300</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I52" s="22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L52" s="16" t="n">
         <v>150</v>
@@ -6070,7 +6054,7 @@
         <v>45785</v>
       </c>
       <c r="I54" s="22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6099,7 +6083,7 @@
         <v>805</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C56" s="22" t="n">
         <v>25144649</v>
@@ -6118,7 +6102,7 @@
         <v>45696</v>
       </c>
       <c r="I56" s="22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6142,10 +6126,10 @@
         <v>35300</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I57" s="22" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6183,7 +6167,7 @@
         <v>45665</v>
       </c>
       <c r="I59" s="22" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6210,7 +6194,7 @@
         <v>45785</v>
       </c>
       <c r="I60" s="22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6237,7 +6221,7 @@
         <v>45755</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6264,7 +6248,7 @@
         <v>45665</v>
       </c>
       <c r="I62" s="22" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6310,7 +6294,7 @@
         <v>45846</v>
       </c>
       <c r="I64" s="22" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6329,7 +6313,7 @@
         <v>126</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C66" s="22" t="s">
         <v>229</v>
@@ -6345,10 +6329,10 @@
         <v>29450</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I66" s="22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6366,7 +6350,7 @@
       </c>
       <c r="G67" s="40" t="n">
         <f aca="false">SUM(G3:G66)</f>
-        <v>1494420</v>
+        <v>1534420</v>
       </c>
       <c r="H67" s="21"/>
       <c r="I67" s="22"/>
@@ -6479,603 +6463,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E65"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="43.11"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>795778727</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>712618128</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>7997082120</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>206</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>799002197</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>302</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>724779438</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>304</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>795141552</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>723701190</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>306</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>795224557</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>401</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>29807634</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>703138775</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>402</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>728325855</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>404</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>712665837</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>405</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>701116277</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>406</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>720334200</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>501</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>705021087</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>502</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>798082750</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>503</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>708822190</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>504</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>718169400</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>505</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>711236179</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>506</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>708860250</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>601</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>722138646</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>602</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>110147006</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>603</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>721967235</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>604</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>723482227</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>605</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>729584979</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>606</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>714994070</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>701</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>743552330</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>702</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>705021087</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>703</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>717982212</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>704</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>741497042</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>705</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>725535858</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>706</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>707947316</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>801</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>724838245</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>802</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>720229325</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>803</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>704498777</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>804</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>796828986</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>805</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>726319801</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>806</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>791229029</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>901</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>702602056</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>902</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>721178178</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>903</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>904</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>727692378</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>905</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>727826667</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>906</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>748908722</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>743853830</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>